--- a/auxiliar_linha_producao_SENAI/Relacoes/Atividades.xlsx
+++ b/auxiliar_linha_producao_SENAI/Relacoes/Atividades.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\auxiliar_linha_producao_SENAI\Relacoes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91CC4B93-B3A3-45CA-BB3C-DDF13CF37B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACC017E9-C3C2-4746-A48B-A3BC98A7253F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>ANA CRISTINA GOMES ARANHA MARCELO</t>
   </si>
@@ -115,6 +126,15 @@
   </si>
   <si>
     <t>N1</t>
+  </si>
+  <si>
+    <t>Maior Nota</t>
+  </si>
+  <si>
+    <t>Menor Nota</t>
+  </si>
+  <si>
+    <t>Média</t>
   </si>
 </sst>
 </file>
@@ -211,7 +231,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -508,15 +528,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4" style="3" customWidth="1"/>
     <col min="2" max="2" width="34.08984375" style="3" customWidth="1"/>
     <col min="3" max="3" width="8.7265625" style="3"/>
+    <col min="9" max="9" width="10.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>27</v>
       </c>
@@ -524,7 +545,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -534,8 +555,15 @@
       <c r="C2" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2">
+        <f>MAX(C3:C28)</f>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -543,8 +571,15 @@
         <v>1</v>
       </c>
       <c r="C3" s="5"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="I3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3">
+        <f>MIN(C3:C28)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -554,8 +589,15 @@
       <c r="C4" s="5">
         <v>34</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4">
+        <f>AVERAGE(C3:C28)</f>
+        <v>41.772727272727273</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -566,7 +608,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -577,7 +619,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -588,7 +630,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -599,7 +641,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -610,7 +652,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -621,7 +663,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -632,7 +674,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -643,7 +685,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -652,7 +694,7 @@
       </c>
       <c r="C13" s="5"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -663,7 +705,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -674,7 +716,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>15</v>
       </c>

--- a/auxiliar_linha_producao_SENAI/Relacoes/Atividades.xlsx
+++ b/auxiliar_linha_producao_SENAI/Relacoes/Atividades.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\auxiliar_linha_producao_SENAI\Relacoes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACC017E9-C3C2-4746-A48B-A3BC98A7253F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F433EBCC-F9A8-406B-B4B8-DE087AEF17D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Avaliação" sheetId="1" r:id="rId1"/>
+    <sheet name="Atividade em Sala" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="36">
   <si>
     <t>ANA CRISTINA GOMES ARANHA MARCELO</t>
   </si>
@@ -135,6 +136,15 @@
   </si>
   <si>
     <t>Média</t>
+  </si>
+  <si>
+    <t>Ok</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>Faltou</t>
   </si>
 </sst>
 </file>
@@ -223,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -237,6 +247,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -560,7 +571,7 @@
       </c>
       <c r="J2">
         <f>MAX(C3:C28)</f>
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -594,7 +605,7 @@
       </c>
       <c r="J4">
         <f>AVERAGE(C3:C28)</f>
-        <v>41.772727272727273</v>
+        <v>42.227272727272727</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
@@ -627,7 +638,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="5">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
@@ -863,4 +874,325 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{901E74B7-7B3A-4A26-9E2C-E9D0F1A7CAAC}">
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="33.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="7">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="26" x14ac:dyDescent="0.35">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/auxiliar_linha_producao_SENAI/Relacoes/Atividades.xlsx
+++ b/auxiliar_linha_producao_SENAI/Relacoes/Atividades.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\auxiliar_linha_producao_SENAI\Relacoes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F433EBCC-F9A8-406B-B4B8-DE087AEF17D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1395E58-4900-4085-9FE8-E0730286720F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="37">
   <si>
     <t>ANA CRISTINA GOMES ARANHA MARCELO</t>
   </si>
@@ -145,6 +145,9 @@
   </si>
   <si>
     <t>Faltou</t>
+  </si>
+  <si>
+    <t>N1/REC</t>
   </si>
 </sst>
 </file>
@@ -233,7 +236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -248,11 +251,32 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -555,6 +579,15 @@
       <c r="B1" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="C1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
@@ -563,8 +596,13 @@
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>29</v>
+      <c r="C2" s="4"/>
+      <c r="D2" s="8">
+        <v>95</v>
+      </c>
+      <c r="E2" s="8">
+        <f>AVERAGE(C2:D2)</f>
+        <v>95</v>
       </c>
       <c r="I2" t="s">
         <v>30</v>
@@ -581,13 +619,22 @@
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="5"/>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0</v>
+      </c>
+      <c r="E3" s="8">
+        <f t="shared" ref="E3:E28" si="0">AVERAGE(C3:D3)</f>
+        <v>0</v>
+      </c>
       <c r="I3" t="s">
         <v>31</v>
       </c>
       <c r="J3">
         <f>MIN(C3:C28)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -600,12 +647,19 @@
       <c r="C4" s="5">
         <v>34</v>
       </c>
+      <c r="D4" s="8">
+        <v>100</v>
+      </c>
+      <c r="E4" s="8">
+        <f t="shared" si="0"/>
+        <v>67</v>
+      </c>
       <c r="I4" t="s">
         <v>32</v>
       </c>
       <c r="J4">
-        <f>AVERAGE(C3:C28)</f>
-        <v>42.227272727272727</v>
+        <f>AVERAGE(E2:E28)</f>
+        <v>51.277777777777779</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
@@ -618,6 +672,13 @@
       <c r="C5" s="5">
         <v>75</v>
       </c>
+      <c r="D5" s="8">
+        <v>100</v>
+      </c>
+      <c r="E5" s="8">
+        <f t="shared" si="0"/>
+        <v>87.5</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
@@ -629,6 +690,13 @@
       <c r="C6" s="5">
         <v>50</v>
       </c>
+      <c r="D6" s="8">
+        <v>95</v>
+      </c>
+      <c r="E6" s="8">
+        <f t="shared" si="0"/>
+        <v>72.5</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
@@ -640,6 +708,13 @@
       <c r="C7" s="5">
         <v>91</v>
       </c>
+      <c r="D7" s="8">
+        <v>100</v>
+      </c>
+      <c r="E7" s="8">
+        <f t="shared" si="0"/>
+        <v>95.5</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
@@ -651,6 +726,13 @@
       <c r="C8" s="5">
         <v>32</v>
       </c>
+      <c r="D8" s="8">
+        <v>95</v>
+      </c>
+      <c r="E8" s="8">
+        <f t="shared" si="0"/>
+        <v>63.5</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
@@ -662,6 +744,13 @@
       <c r="C9" s="5">
         <v>16</v>
       </c>
+      <c r="D9" s="8">
+        <v>100</v>
+      </c>
+      <c r="E9" s="8">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
@@ -673,6 +762,13 @@
       <c r="C10" s="5">
         <v>36</v>
       </c>
+      <c r="D10" s="8">
+        <v>90</v>
+      </c>
+      <c r="E10" s="8">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
@@ -684,6 +780,13 @@
       <c r="C11" s="5">
         <v>60</v>
       </c>
+      <c r="D11" s="8">
+        <v>0</v>
+      </c>
+      <c r="E11" s="8">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
@@ -695,6 +798,13 @@
       <c r="C12" s="5">
         <v>70</v>
       </c>
+      <c r="D12" s="8">
+        <v>0</v>
+      </c>
+      <c r="E12" s="8">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
@@ -703,7 +813,16 @@
       <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5"/>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0</v>
+      </c>
+      <c r="E13" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
@@ -715,6 +834,13 @@
       <c r="C14" s="5">
         <v>30</v>
       </c>
+      <c r="D14" s="8">
+        <v>95</v>
+      </c>
+      <c r="E14" s="8">
+        <f t="shared" si="0"/>
+        <v>62.5</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
@@ -726,6 +852,13 @@
       <c r="C15" s="5">
         <v>30</v>
       </c>
+      <c r="D15" s="8">
+        <v>95</v>
+      </c>
+      <c r="E15" s="8">
+        <f t="shared" si="0"/>
+        <v>62.5</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
@@ -734,9 +867,18 @@
       <c r="B16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="5"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="8">
+        <v>0</v>
+      </c>
+      <c r="E16" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -746,8 +888,15 @@
       <c r="C17" s="5">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D17" s="8">
+        <v>95</v>
+      </c>
+      <c r="E17" s="8">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -757,8 +906,15 @@
       <c r="C18" s="5">
         <v>21</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D18" s="8">
+        <v>0</v>
+      </c>
+      <c r="E18" s="8">
+        <f t="shared" si="0"/>
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -768,8 +924,15 @@
       <c r="C19" s="5">
         <v>40</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D19" s="8">
+        <v>100</v>
+      </c>
+      <c r="E19" s="8">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -779,8 +942,15 @@
       <c r="C20" s="5">
         <v>37</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D20" s="8">
+        <v>100</v>
+      </c>
+      <c r="E20" s="8">
+        <f t="shared" si="0"/>
+        <v>68.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -790,8 +960,15 @@
       <c r="C21" s="5">
         <v>26</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D21" s="8">
+        <v>100</v>
+      </c>
+      <c r="E21" s="8">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -801,8 +978,15 @@
       <c r="C22" s="5">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D22" s="8">
+        <v>0</v>
+      </c>
+      <c r="E22" s="8">
+        <f t="shared" si="0"/>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -812,17 +996,33 @@
       <c r="C23" s="5">
         <v>76</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D23" s="8">
+        <v>100</v>
+      </c>
+      <c r="E23" s="8">
+        <f t="shared" si="0"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="5"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C24" s="5">
+        <v>0</v>
+      </c>
+      <c r="D24" s="8">
+        <v>0</v>
+      </c>
+      <c r="E24" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -832,8 +1032,15 @@
       <c r="C25" s="5">
         <v>50</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D25" s="8">
+        <v>100</v>
+      </c>
+      <c r="E25" s="8">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -843,8 +1050,15 @@
       <c r="C26" s="5">
         <v>85</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D26" s="8">
+        <v>100</v>
+      </c>
+      <c r="E26" s="8">
+        <f t="shared" si="0"/>
+        <v>92.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -854,8 +1068,15 @@
       <c r="C27" s="6">
         <v>37</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D27" s="8">
+        <v>85</v>
+      </c>
+      <c r="E27" s="8">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -865,9 +1086,21 @@
       <c r="C28" s="5">
         <v>5</v>
       </c>
+      <c r="D28" s="8">
+        <v>0</v>
+      </c>
+      <c r="E28" s="8">
+        <f t="shared" si="0"/>
+        <v>2.5</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C3:C28">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
+      <formula>50</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:E28">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>50</formula>
     </cfRule>
